--- a/public/templates/roster-template.xlsx
+++ b/public/templates/roster-template.xlsx
@@ -932,7 +932,7 @@
         <v>71</v>
       </c>
       <c r="P2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="Q2">
         <v>62</v>
@@ -1027,7 +1027,7 @@
         <v>77</v>
       </c>
       <c r="P3">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q3">
         <v>88</v>
